--- a/Mapeo Alumno.xlsx
+++ b/Mapeo Alumno.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>ALUMNO</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>Carlos Camacho</t>
-  </si>
-  <si>
-    <t>ccamacho@gmail.com</t>
   </si>
   <si>
     <t>Calle Landivar 400</t>
@@ -647,9 +644,7 @@
       <c r="C7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="5">
         <v>37245</v>
       </c>
@@ -660,7 +655,7 @@
         <v>12</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>15</v>
@@ -674,10 +669,10 @@
         <v>388</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="E8" s="5">
         <v>38515</v>
@@ -689,7 +684,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>15</v>
@@ -700,10 +695,9 @@
     <hyperlink ref="D4" r:id="rId1"/>
     <hyperlink ref="D5" r:id="rId2"/>
     <hyperlink ref="D6" r:id="rId3"/>
-    <hyperlink ref="D7" r:id="rId4"/>
-    <hyperlink ref="D8" r:id="rId5"/>
+    <hyperlink ref="D8" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId6"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId5"/>
 </worksheet>
 </file>